--- a/artfynd/A 62105-2022 artfynd.xlsx
+++ b/artfynd/A 62105-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62105-2022 artfynd.xlsx
+++ b/artfynd/A 62105-2022 artfynd.xlsx
@@ -675,19 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104986985</v>
+        <v>104986982</v>
       </c>
       <c r="B2" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501512</v>
+        <v>501388</v>
       </c>
       <c r="R2" t="n">
-        <v>6629412</v>
+        <v>6629662</v>
       </c>
       <c r="S2" t="n">
         <v>20</v>
@@ -782,19 +777,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104986987</v>
+        <v>104986983</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +812,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501373</v>
+        <v>501493</v>
       </c>
       <c r="R3" t="n">
-        <v>6629597</v>
+        <v>6629535</v>
       </c>
       <c r="S3" t="n">
         <v>20</v>
@@ -889,19 +879,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104986982</v>
+        <v>104986984</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -929,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501388</v>
+        <v>501523</v>
       </c>
       <c r="R4" t="n">
-        <v>6629662</v>
+        <v>6629491</v>
       </c>
       <c r="S4" t="n">
         <v>20</v>
@@ -996,19 +981,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104986986</v>
+        <v>104986985</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501463</v>
+        <v>501512</v>
       </c>
       <c r="R5" t="n">
-        <v>6629492</v>
+        <v>6629412</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1103,19 +1083,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>104986984</v>
+        <v>104986986</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1143,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501523</v>
+        <v>501463</v>
       </c>
       <c r="R6" t="n">
-        <v>6629491</v>
+        <v>6629492</v>
       </c>
       <c r="S6" t="n">
         <v>20</v>
@@ -1210,19 +1185,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>104986983</v>
+        <v>104986987</v>
       </c>
       <c r="B7" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1250,10 +1220,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>501493</v>
+        <v>501373</v>
       </c>
       <c r="R7" t="n">
-        <v>6629535</v>
+        <v>6629597</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1320,12 +1290,7 @@
         <v>104986989</v>
       </c>
       <c r="B8" t="n">
-        <v>57624</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Behöver inte valideras</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>

--- a/artfynd/A 62105-2022 artfynd.xlsx
+++ b/artfynd/A 62105-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986982</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986983</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986984</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986985</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,6 +1207,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986986</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1284,6 +1314,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986987</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1381,8 +1416,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104986989</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>